--- a/htr-CDA/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-CDA/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T13:15:07+00:00</t>
+    <t>2025-02-20T09:25:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-CDA/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-CDA/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T09:25:35+00:00</t>
+    <t>2025-02-23T14:32:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-CDA/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/htr-CDA/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:32:26+00:00</t>
+    <t>2025-02-24T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
